--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.82266664241683</v>
+        <v>13.29618332939274</v>
       </c>
       <c r="D2" t="n">
-        <v>59.94147750461428</v>
+        <v>9.740490094499821</v>
       </c>
       <c r="E2" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F2" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>90.4438417443493</v>
+        <v>14.69712428345676</v>
       </c>
       <c r="D3" t="n">
-        <v>68.39182931638383</v>
+        <v>11.11367226391237</v>
       </c>
       <c r="E3" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F3" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.2889480350609</v>
+        <v>12.5594540556974</v>
       </c>
       <c r="D4" t="n">
-        <v>63.10751232743241</v>
+        <v>10.25497075320777</v>
       </c>
       <c r="E4" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F4" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>93.944761059469</v>
+        <v>15.26602367216371</v>
       </c>
       <c r="D5" t="n">
-        <v>88.42923221013832</v>
+        <v>14.36975023414748</v>
       </c>
       <c r="E5" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F5" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>82.94944190794602</v>
+        <v>13.47928431004123</v>
       </c>
       <c r="D6" t="n">
-        <v>73.68153348669756</v>
+        <v>11.97324919158835</v>
       </c>
       <c r="E6" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F6" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>72.77598701746378</v>
+        <v>11.82609789033786</v>
       </c>
       <c r="D7" t="n">
-        <v>55.06381993378164</v>
+        <v>8.947870739239518</v>
       </c>
       <c r="E7" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F7" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>84.20464388672011</v>
+        <v>13.68325463159202</v>
       </c>
       <c r="D8" t="n">
-        <v>62.12239817936486</v>
+        <v>10.09488970414679</v>
       </c>
       <c r="E8" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F8" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>69.84976037419737</v>
+        <v>11.35058606080707</v>
       </c>
       <c r="D9" t="n">
-        <v>54.53274262647601</v>
+        <v>8.861570676802353</v>
       </c>
       <c r="E9" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F9" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>96.00188626053639</v>
+        <v>15.60030651733716</v>
       </c>
       <c r="D10" t="n">
-        <v>73.49411506376198</v>
+        <v>11.94279369786132</v>
       </c>
       <c r="E10" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F10" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>70.17303993497954</v>
+        <v>11.40311898943418</v>
       </c>
       <c r="D11" t="n">
-        <v>50.0934905999498</v>
+        <v>8.140192222491843</v>
       </c>
       <c r="E11" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F11" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>97.08181665561406</v>
+        <v>15.77579520653729</v>
       </c>
       <c r="D12" t="n">
-        <v>94.38397580785103</v>
+        <v>15.33739606877579</v>
       </c>
       <c r="E12" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F12" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>92.92888225825158</v>
+        <v>15.10094336696588</v>
       </c>
       <c r="D13" t="n">
-        <v>89.59979379813608</v>
+        <v>14.55996649219711</v>
       </c>
       <c r="E13" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F13" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>70.3723904529204</v>
+        <v>11.43551344859956</v>
       </c>
       <c r="D14" t="n">
-        <v>59.32526177803298</v>
+        <v>9.640355038930359</v>
       </c>
       <c r="E14" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F14" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>97.18935206578375</v>
+        <v>15.79326971068986</v>
       </c>
       <c r="D15" t="n">
-        <v>74.8206234195418</v>
+        <v>12.15835130567554</v>
       </c>
       <c r="E15" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F15" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>82.73475840478154</v>
+        <v>13.444398240777</v>
       </c>
       <c r="D16" t="n">
-        <v>60.29742763483587</v>
+        <v>9.798331990660829</v>
       </c>
       <c r="E16" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F16" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>85.79980076463839</v>
+        <v>13.94246762425374</v>
       </c>
       <c r="D17" t="n">
-        <v>63.3089121939779</v>
+        <v>10.28769823152141</v>
       </c>
       <c r="E17" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F17" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>78.78766094915679</v>
+        <v>12.80299490423798</v>
       </c>
       <c r="D18" t="n">
-        <v>75.20639491790105</v>
+        <v>12.22103917415892</v>
       </c>
       <c r="E18" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F18" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>58.53359470488049</v>
+        <v>9.511709139543079</v>
       </c>
       <c r="D19" t="n">
-        <v>37.8291567623252</v>
+        <v>6.147237973877845</v>
       </c>
       <c r="E19" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F19" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>59.24328038262884</v>
+        <v>9.627033062177187</v>
       </c>
       <c r="D20" t="n">
-        <v>46.78823673379372</v>
+        <v>7.60308846924148</v>
       </c>
       <c r="E20" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F20" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>56.70437053282157</v>
+        <v>9.214460211583505</v>
       </c>
       <c r="D21" t="n">
-        <v>42.09191263502485</v>
+        <v>6.839935803191539</v>
       </c>
       <c r="E21" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F21" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>56.3043063794558</v>
+        <v>9.149449786661567</v>
       </c>
       <c r="D22" t="n">
-        <v>39.48467696885933</v>
+        <v>6.416260007439642</v>
       </c>
       <c r="E22" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F22" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>67.91269429184661</v>
+        <v>11.03581282242507</v>
       </c>
       <c r="D23" t="n">
-        <v>45.67762788158869</v>
+        <v>7.422614530758162</v>
       </c>
       <c r="E23" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F23" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>59.00028957411536</v>
+        <v>9.587547055793745</v>
       </c>
       <c r="D24" t="n">
-        <v>36.95632906525225</v>
+        <v>6.005403473103491</v>
       </c>
       <c r="E24" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F24" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>84.83028546338906</v>
+        <v>13.78492138780072</v>
       </c>
       <c r="D25" t="n">
-        <v>62.63030694469654</v>
+        <v>10.17742487851319</v>
       </c>
       <c r="E25" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F25" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>47.82622791988499</v>
+        <v>7.771762036981311</v>
       </c>
       <c r="D26" t="n">
-        <v>31.71179906885851</v>
+        <v>5.153167348689508</v>
       </c>
       <c r="E26" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F26" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>73.8891624434812</v>
+        <v>12.00698889706569</v>
       </c>
       <c r="D27" t="n">
-        <v>51.59850471562997</v>
+        <v>8.384757016289871</v>
       </c>
       <c r="E27" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F27" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>59.34237321809883</v>
+        <v>9.64313564794106</v>
       </c>
       <c r="D28" t="n">
-        <v>51.98450518378665</v>
+        <v>8.44748209236533</v>
       </c>
       <c r="E28" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F28" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>48.2975242960672</v>
+        <v>7.848347698110921</v>
       </c>
       <c r="D29" t="n">
-        <v>35.33498070095155</v>
+        <v>5.741934363904628</v>
       </c>
       <c r="E29" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F29" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>70.19171316860628</v>
+        <v>11.40615338989852</v>
       </c>
       <c r="D30" t="n">
-        <v>68.8902643746368</v>
+        <v>11.19466796087848</v>
       </c>
       <c r="E30" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F30" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>60.78057520741028</v>
+        <v>9.87684347120417</v>
       </c>
       <c r="D31" t="n">
-        <v>38.26292096779404</v>
+        <v>6.217724657266531</v>
       </c>
       <c r="E31" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F31" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>81.87954849602593</v>
+        <v>13.30542663060421</v>
       </c>
       <c r="D32" t="n">
-        <v>80.28617928820741</v>
+        <v>13.0465041343337</v>
       </c>
       <c r="E32" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F32" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>46.82269016012328</v>
+        <v>7.608687151020034</v>
       </c>
       <c r="D33" t="n">
-        <v>42.13131641758797</v>
+        <v>6.846338917858046</v>
       </c>
       <c r="E33" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F33" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>78.23403200317382</v>
+        <v>12.71303020051575</v>
       </c>
       <c r="D34" t="n">
-        <v>53.71535127271141</v>
+        <v>8.728744581815604</v>
       </c>
       <c r="E34" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F34" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>61.93967036642857</v>
+        <v>10.06519643454464</v>
       </c>
       <c r="D35" t="n">
-        <v>60.3416250302998</v>
+        <v>9.805514067423717</v>
       </c>
       <c r="E35" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F35" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>48.4693972214024</v>
+        <v>7.876277048477889</v>
       </c>
       <c r="D36" t="n">
-        <v>47.37123910038521</v>
+        <v>7.697826353812597</v>
       </c>
       <c r="E36" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F36" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>67.58921877914906</v>
+        <v>10.98324805161172</v>
       </c>
       <c r="D37" t="n">
-        <v>65.82563791851221</v>
+        <v>10.69666616175824</v>
       </c>
       <c r="E37" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F37" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>37.53558875059363</v>
+        <v>6.099533171971465</v>
       </c>
       <c r="D38" t="n">
-        <v>32.26776033231945</v>
+        <v>5.24351105400191</v>
       </c>
       <c r="E38" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F38" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>26.73665725154749</v>
+        <v>4.344706803376467</v>
       </c>
       <c r="D39" t="n">
-        <v>14.30729905482726</v>
+        <v>2.32493609640943</v>
       </c>
       <c r="E39" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F39" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>49.14824267170755</v>
+        <v>7.986589434152477</v>
       </c>
       <c r="D40" t="n">
-        <v>27.70136619174023</v>
+        <v>4.501472006157788</v>
       </c>
       <c r="E40" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F40" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>72.38294097907996</v>
+        <v>11.76222790910049</v>
       </c>
       <c r="D41" t="n">
-        <v>70.32010436259654</v>
+        <v>11.42701695892194</v>
       </c>
       <c r="E41" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F41" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>63.83091044493174</v>
+        <v>10.37252294730141</v>
       </c>
       <c r="D42" t="n">
-        <v>37.07263674002252</v>
+        <v>6.024303470253659</v>
       </c>
       <c r="E42" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F42" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>77.46112296183853</v>
+        <v>12.58743248129876</v>
       </c>
       <c r="D43" t="n">
-        <v>47.29835992112544</v>
+        <v>7.685983487182884</v>
       </c>
       <c r="E43" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F43" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>49.02876903578105</v>
+        <v>7.967174968314421</v>
       </c>
       <c r="D44" t="n">
-        <v>47.27731040647348</v>
+        <v>7.68256294105194</v>
       </c>
       <c r="E44" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F44" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>23.58181418840198</v>
+        <v>3.832044805615321</v>
       </c>
       <c r="D45" t="n">
-        <v>2.64609836311713</v>
+        <v>0.4299909840065336</v>
       </c>
       <c r="E45" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F45" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>19.99278589338137</v>
+        <v>3.248827707674473</v>
       </c>
       <c r="D46" t="n">
-        <v>9.608541615734316</v>
+        <v>1.561388012556826</v>
       </c>
       <c r="E46" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F46" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>63.24611567591632</v>
+        <v>10.2774937973364</v>
       </c>
       <c r="D47" t="n">
-        <v>61.0682142194963</v>
+        <v>9.923584810668149</v>
       </c>
       <c r="E47" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F47" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>71.83261902749697</v>
+        <v>11.67280059196826</v>
       </c>
       <c r="D48" t="n">
-        <v>69.43839231343154</v>
+        <v>11.28373875093262</v>
       </c>
       <c r="E48" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F48" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>73.94024572237802</v>
+        <v>12.01528992988643</v>
       </c>
       <c r="D49" t="n">
-        <v>40.28621160138922</v>
+        <v>6.546509385225749</v>
       </c>
       <c r="E49" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F49" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>56.7209225949529</v>
+        <v>9.217149921679846</v>
       </c>
       <c r="D50" t="n">
-        <v>54.20225318650825</v>
+        <v>8.80786614280759</v>
       </c>
       <c r="E50" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F50" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>61.68193911030642</v>
+        <v>10.02331510542479</v>
       </c>
       <c r="D51" t="n">
-        <v>27.18831450746466</v>
+        <v>4.418101107463008</v>
       </c>
       <c r="E51" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F51" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>47.48597390849746</v>
+        <v>7.716470760130838</v>
       </c>
       <c r="D52" t="n">
-        <v>45.02377024546782</v>
+        <v>7.316362664888522</v>
       </c>
       <c r="E52" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F52" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>72.25378840839745</v>
+        <v>11.74124061636459</v>
       </c>
       <c r="D53" t="n">
-        <v>69.50810434962918</v>
+        <v>11.29506695681474</v>
       </c>
       <c r="E53" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F53" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>55.73535977581596</v>
+        <v>9.056995963570094</v>
       </c>
       <c r="D54" t="n">
-        <v>52.94075849506276</v>
+        <v>8.602873255447699</v>
       </c>
       <c r="E54" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F54" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>71.3983034839264</v>
+        <v>11.60222431613804</v>
       </c>
       <c r="D55" t="n">
-        <v>32.21408531384176</v>
+        <v>5.234788863499285</v>
       </c>
       <c r="E55" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F55" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>56.63169669159938</v>
+        <v>9.2026507123849</v>
       </c>
       <c r="D56" t="n">
-        <v>17.23856936191476</v>
+        <v>2.801267521311149</v>
       </c>
       <c r="E56" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F56" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>51.77188164464172</v>
+        <v>8.412930767254281</v>
       </c>
       <c r="D57" t="n">
-        <v>14.35571288962968</v>
+        <v>2.332803344564822</v>
       </c>
       <c r="E57" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F57" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>56.5042063658954</v>
+        <v>9.181933534458002</v>
       </c>
       <c r="D58" t="n">
-        <v>49.21607686744466</v>
+        <v>7.997612490959758</v>
       </c>
       <c r="E58" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F58" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>22.62762462385016</v>
+        <v>3.676989001375652</v>
       </c>
       <c r="D59" t="n">
-        <v>21.08439375912849</v>
+        <v>3.42621398585838</v>
       </c>
       <c r="E59" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F59" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>79.12323172621397</v>
+        <v>12.85752515550977</v>
       </c>
       <c r="D60" t="n">
-        <v>40.16690671258701</v>
+        <v>6.52712234079539</v>
       </c>
       <c r="E60" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F60" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>65.41305633843474</v>
+        <v>10.62962165499565</v>
       </c>
       <c r="D61" t="n">
-        <v>54.85333981526456</v>
+        <v>8.913667719980491</v>
       </c>
       <c r="E61" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F61" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>48.07936694823861</v>
+        <v>7.812897129088774</v>
       </c>
       <c r="D62" t="n">
-        <v>38.70143814935486</v>
+        <v>6.288983699270165</v>
       </c>
       <c r="E62" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F62" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>56.69230811564488</v>
+        <v>9.212500068792295</v>
       </c>
       <c r="D63" t="n">
-        <v>45.21676188710946</v>
+        <v>7.347723806655288</v>
       </c>
       <c r="E63" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F63" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>26.14620650749529</v>
+        <v>4.248758557467985</v>
       </c>
       <c r="D64" t="n">
-        <v>18.8694344259587</v>
+        <v>3.066283094218289</v>
       </c>
       <c r="E64" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F64" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>63.7390451520259</v>
+        <v>10.35759483720421</v>
       </c>
       <c r="D65" t="n">
-        <v>26.92008545525578</v>
+        <v>4.374513886479065</v>
       </c>
       <c r="E65" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F65" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>32.01918644433607</v>
+        <v>5.203117797204611</v>
       </c>
       <c r="D66" t="n">
-        <v>15.76750354033447</v>
+        <v>2.562219325304352</v>
       </c>
       <c r="E66" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F66" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>77.45271371383485</v>
+        <v>12.58606597849816</v>
       </c>
       <c r="D67" t="n">
-        <v>62.81721562497952</v>
+        <v>10.20779753905917</v>
       </c>
       <c r="E67" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F67" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>80.46063815920547</v>
+        <v>13.07485370087089</v>
       </c>
       <c r="D68" t="n">
-        <v>42.65810555970042</v>
+        <v>6.931942153451318</v>
       </c>
       <c r="E68" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F68" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>73.18392609093713</v>
+        <v>11.89238798977729</v>
       </c>
       <c r="D69" t="n">
-        <v>52.51243239039261</v>
+        <v>8.5332702634388</v>
       </c>
       <c r="E69" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F69" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>44.96393043129015</v>
+        <v>7.30663869508465</v>
       </c>
       <c r="D70" t="n">
-        <v>19.66629193693495</v>
+        <v>3.195772439751929</v>
       </c>
       <c r="E70" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F70" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>66.89399481112939</v>
+        <v>10.87027415680853</v>
       </c>
       <c r="D71" t="n">
-        <v>34.42479135238464</v>
+        <v>5.594028594762505</v>
       </c>
       <c r="E71" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F71" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>79.47895221256024</v>
+        <v>12.91532973454104</v>
       </c>
       <c r="D72" t="n">
-        <v>45.18733834131879</v>
+        <v>7.342942480464304</v>
       </c>
       <c r="E72" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F72" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>80.72165730003388</v>
+        <v>13.11726931125551</v>
       </c>
       <c r="D73" t="n">
-        <v>59.72245692047516</v>
+        <v>9.704899249577213</v>
       </c>
       <c r="E73" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F73" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>48.382565563543</v>
+        <v>7.862166904075737</v>
       </c>
       <c r="D74" t="n">
-        <v>8.910044269749102</v>
+        <v>1.447882193834229</v>
       </c>
       <c r="E74" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F74" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>71.75734706135781</v>
+        <v>11.66056889747064</v>
       </c>
       <c r="D75" t="n">
-        <v>45.88451687540023</v>
+        <v>7.456233992252538</v>
       </c>
       <c r="E75" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F75" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>52.57807507503323</v>
+        <v>8.5439371996929</v>
       </c>
       <c r="D76" t="n">
-        <v>19.90490010050225</v>
+        <v>3.234546266331616</v>
       </c>
       <c r="E76" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F76" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>80.58088992209409</v>
+        <v>13.09439461234029</v>
       </c>
       <c r="D77" t="n">
-        <v>50.56854531750038</v>
+        <v>8.217388614093812</v>
       </c>
       <c r="E77" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F77" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>89.94737079679224</v>
+        <v>14.61644775447874</v>
       </c>
       <c r="D78" t="n">
-        <v>59.70669048681972</v>
+        <v>9.702337204108204</v>
       </c>
       <c r="E78" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F78" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>58.63857269510405</v>
+        <v>9.528768062954407</v>
       </c>
       <c r="D79" t="n">
-        <v>14.21424466398199</v>
+        <v>2.309814757897073</v>
       </c>
       <c r="E79" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F79" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>86.69851361728539</v>
+        <v>14.08850846280887</v>
       </c>
       <c r="D80" t="n">
-        <v>58.04714725073556</v>
+        <v>9.432661428244529</v>
       </c>
       <c r="E80" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F80" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>62.81941024620412</v>
+        <v>10.20815416500817</v>
       </c>
       <c r="D81" t="n">
-        <v>21.24591463996994</v>
+        <v>3.452461128995115</v>
       </c>
       <c r="E81" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F81" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>70.60724546194626</v>
+        <v>11.47367738756627</v>
       </c>
       <c r="D82" t="n">
-        <v>51.0881892972449</v>
+        <v>8.301830760802297</v>
       </c>
       <c r="E82" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F82" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>75.15117416072437</v>
+        <v>12.21206580111771</v>
       </c>
       <c r="D83" t="n">
-        <v>37.41755497913491</v>
+        <v>6.080352684109422</v>
       </c>
       <c r="E83" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F83" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>68.97657469609409</v>
+        <v>11.20869338811529</v>
       </c>
       <c r="D84" t="n">
-        <v>44.93414313099932</v>
+        <v>7.30179825878739</v>
       </c>
       <c r="E84" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F84" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>71.64327855789215</v>
+        <v>11.64203276565747</v>
       </c>
       <c r="D85" t="n">
-        <v>28.26224186669512</v>
+        <v>4.592614303337958</v>
       </c>
       <c r="E85" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F85" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3168,16 +3168,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>88.60405690774941</v>
+        <v>14.39815924750928</v>
       </c>
       <c r="D86" t="n">
-        <v>53.66320862662722</v>
+        <v>8.720271401826922</v>
       </c>
       <c r="E86" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F86" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>74.058501707848</v>
+        <v>12.0345065275253</v>
       </c>
       <c r="D87" t="n">
-        <v>29.51459149490487</v>
+        <v>4.796121117922042</v>
       </c>
       <c r="E87" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F87" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3232,16 +3232,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>74.4529630781677</v>
+        <v>12.09860650020225</v>
       </c>
       <c r="D88" t="n">
-        <v>41.66177665067108</v>
+        <v>6.77003870573405</v>
       </c>
       <c r="E88" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F88" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>82.77269614768436</v>
+        <v>13.45056312399871</v>
       </c>
       <c r="D89" t="n">
-        <v>59.35395455999859</v>
+        <v>9.645017615999771</v>
       </c>
       <c r="E89" t="n">
-        <v>17.48089933191122</v>
+        <v>2.840646141435573</v>
       </c>
       <c r="F89" t="n">
-        <v>19.35794882316338</v>
+        <v>3.145666683764048</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
